--- a/data/trans_orig/IP31A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31A-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43942</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58777</t>
+          <t>59128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>43986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92400</t>
+          <t>92010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112471</t>
+          <t>113500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15908</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29022</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30443</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>48538</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19912</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40493</t>
+          <t>39449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>30776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>32636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46355</t>
+          <t>45936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67274</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86926</t>
+          <t>87123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,12%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22373</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44461</t>
+          <t>44198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>23030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37571</t>
+          <t>38127</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51728</t>
+          <t>52658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>57311</t>
+          <t>56735</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>76227</t>
+          <t>75321</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29416</t>
+          <t>29726</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>50633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39822</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55288</t>
+          <t>54911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65553</t>
+          <t>64684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90757</t>
+          <t>89848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107912</t>
+          <t>109279</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71016</t>
+          <t>69852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90813</t>
+          <t>90730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163255</t>
+          <t>164437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193578</t>
+          <t>194291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48662</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49245</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67357</t>
+          <t>67548</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>93217</t>
+          <t>93017</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35251</t>
+          <t>34914</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>32266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47068</t>
+          <t>47123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44302</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>59917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82169</t>
+          <t>80394</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103511</t>
+          <t>103071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28775</t>
+          <t>29068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36930</t>
+          <t>37082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55104</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30904</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40526</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>31688</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50445</t>
+          <t>51117</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>69734</t>
+          <t>69557</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49786</t>
+          <t>50473</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71445</t>
+          <t>72811</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>100738</t>
+          <t>99503</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>122318</t>
+          <t>122675</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>155666</t>
+          <t>155600</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>200994</t>
+          <t>202940</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>245472</t>
+          <t>246114</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>263030</t>
+          <t>265363</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>302331</t>
+          <t>302619</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>273787</t>
+          <t>274818</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>314040</t>
+          <t>311047</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>549808</t>
+          <t>550240</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>603787</t>
+          <t>603434</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>135516</t>
+          <t>134429</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>169993</t>
+          <t>169384</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>114504</t>
+          <t>114651</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>148046</t>
+          <t>146474</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>258984</t>
+          <t>260271</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>305145</t>
+          <t>308146</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>27994</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>28346</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>30964</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>51043</t>
+          <t>49824</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9149</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>44647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>31776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45380</t>
+          <t>44901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66209</t>
+          <t>66538</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85705</t>
+          <t>85961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24750</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>34634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>52246</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>38395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52422</t>
+          <t>52016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41543</t>
+          <t>41696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56321</t>
+          <t>56426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83270</t>
+          <t>83472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>104625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20919</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>26294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43902</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21085</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>20877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36205</t>
+          <t>36709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29252</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43421</t>
+          <t>43923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>44302</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63846</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>83565</t>
+          <t>84431</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28985</t>
+          <t>28984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48330</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34342</t>
+          <t>33730</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37080</t>
+          <t>37152</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56857</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>59428</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86238</t>
+          <t>85043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95186</t>
+          <t>95728</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83300</t>
+          <t>82283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105471</t>
+          <t>106277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163790</t>
+          <t>164738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194937</t>
+          <t>198816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>32390</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50467</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32122</t>
+          <t>32105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50492</t>
+          <t>50122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67509</t>
+          <t>68050</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>95738</t>
+          <t>94334</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>19091</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28926</t>
+          <t>28579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31258</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>33116</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52308</t>
+          <t>53060</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46418</t>
+          <t>46872</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64773</t>
+          <t>65183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54434</t>
+          <t>54160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72188</t>
+          <t>72484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106225</t>
+          <t>107398</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>131841</t>
+          <t>132190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>27641</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>44411</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>17753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32946</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50057</t>
+          <t>50762</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72864</t>
+          <t>72239</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14158</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24539</t>
+          <t>24020</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>24666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7907,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>27261</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>40283</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>48559</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>65803</t>
+          <t>66429</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,27%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20937</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>70997</t>
+          <t>69815</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>98830</t>
+          <t>97616</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>110638</t>
+          <t>110712</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>143489</t>
+          <t>144822</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>189565</t>
+          <t>188848</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>232942</t>
+          <t>233683</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>265041</t>
+          <t>263322</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>303285</t>
+          <t>302596</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>297852</t>
+          <t>297839</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>336931</t>
+          <t>337525</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>571900</t>
+          <t>574292</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>628499</t>
+          <t>627888</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>139503</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>175440</t>
+          <t>175045</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>116679</t>
+          <t>118153</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>151337</t>
+          <t>150526</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>267524</t>
+          <t>267888</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>315423</t>
+          <t>314694</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27245</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47216</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>33607</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>47371</t>
+          <t>47297</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>72762</t>
+          <t>72055</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20879</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>28323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43202</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>34929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68868</t>
+          <t>67749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88004</t>
+          <t>87839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25549</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26871</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31543</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>48722</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>13799</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61271</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45122</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60349</t>
+          <t>59867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97091</t>
+          <t>96519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117004</t>
+          <t>117549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>31996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48211</t>
+          <t>48562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>20282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39866</t>
+          <t>39875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>48258</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66055</t>
+          <t>65882</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24631</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40058</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>39604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60369</t>
+          <t>60360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83574</t>
+          <t>82527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104203</t>
+          <t>104259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>80473</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102139</t>
+          <t>102651</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>170593</t>
+          <t>171352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201815</t>
+          <t>200821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43664</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64570</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43320</t>
+          <t>42757</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>62938</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91765</t>
+          <t>91827</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120005</t>
+          <t>120318</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,12 +11184,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22487</t>
+          <t>22512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70579</t>
+          <t>71413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58405</t>
+          <t>59353</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76946</t>
+          <t>78229</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117821</t>
+          <t>116040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142551</t>
+          <t>141844</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21973</t>
+          <t>22001</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>37369</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38053</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49554</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71631</t>
+          <t>73113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31620</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>29467</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>39272</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48657</t>
+          <t>48723</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>65715</t>
+          <t>65515</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>23454</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>39723</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48724</t>
+          <t>49098</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>70891</t>
+          <t>71860</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>66509</t>
+          <t>65591</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>93110</t>
+          <t>92665</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>122309</t>
+          <t>122330</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>156957</t>
+          <t>159539</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>275180</t>
+          <t>276706</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314413</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>302445</t>
+          <t>302017</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>342309</t>
+          <t>341936</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>588398</t>
+          <t>585680</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>641747</t>
+          <t>638301</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>133018</t>
+          <t>133586</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>167414</t>
+          <t>167523</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>137172</t>
+          <t>140344</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>172853</t>
+          <t>173729</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>284112</t>
+          <t>282296</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>329737</t>
+          <t>331326</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>61860</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>31794</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>53418</t>
+          <t>53284</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>76514</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>106350</t>
+          <t>108889</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
